--- a/research/traditional_assets/database/data/singapore/singapore_software_internet.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_software_internet.xlsx
@@ -587,23 +587,26 @@
           <t>Software (Internet)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.0738</v>
+      </c>
       <c r="G2">
-        <v>-0.9791666666666665</v>
+        <v>-0.2388379204892966</v>
       </c>
       <c r="H2">
-        <v>-1.704166666666667</v>
+        <v>-0.2395514780835882</v>
       </c>
       <c r="I2">
-        <v>-1.413308268398423</v>
+        <v>-0.2872945515353514</v>
       </c>
       <c r="J2">
-        <v>-1.413308268398423</v>
+        <v>-0.2872945515353514</v>
       </c>
       <c r="K2">
-        <v>-4.3</v>
+        <v>-2.85</v>
       </c>
       <c r="L2">
-        <v>-1.791666666666667</v>
+        <v>-0.290519877675841</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -632,59 +635,68 @@
       <c r="V2">
         <v>0</v>
       </c>
+      <c r="W2">
+        <v>-0.3421368547418968</v>
+      </c>
       <c r="X2">
-        <v>0.05946736856438736</v>
+        <v>0.1136701707817108</v>
+      </c>
+      <c r="Y2">
+        <v>-0.4558070255236075</v>
       </c>
       <c r="Z2">
-        <v>247.4425579303077</v>
+        <v>6.899715504978664</v>
       </c>
       <c r="AA2">
-        <v>-349.7126130765597</v>
+        <v>-1.982250671724356</v>
       </c>
       <c r="AB2">
-        <v>0.0594457175453639</v>
+        <v>0.1136614249837494</v>
       </c>
       <c r="AC2">
-        <v>-349.7720587941051</v>
+        <v>-2.095912096708106</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0.009699220781075019</v>
+        <v>0.001797752808988764</v>
       </c>
       <c r="AF2">
-        <v>0.009699220781075019</v>
+        <v>0.001797752808988764</v>
       </c>
       <c r="AG2">
-        <v>0.009699220781075019</v>
+        <v>0.001797752808988764</v>
       </c>
       <c r="AH2">
-        <v>0.0006419201758652632</v>
+        <v>0.0004309300008079938</v>
       </c>
       <c r="AI2">
-        <v>0.001171446029915086</v>
+        <v>1</v>
       </c>
       <c r="AJ2">
-        <v>0.0006419201758652632</v>
+        <v>0.0004309300008079938</v>
       </c>
       <c r="AK2">
-        <v>0.001171446029915086</v>
+        <v>1</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="AM2">
-        <v>-0.05</v>
+        <v>-0.015</v>
       </c>
       <c r="AN2">
         <v>-0</v>
       </c>
+      <c r="AO2">
+        <v>-469.9999999999999</v>
+      </c>
       <c r="AP2">
-        <v>-0.004162755700032197</v>
+        <v>-0.0008735436389644139</v>
       </c>
       <c r="AQ2">
-        <v>68</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3">
@@ -703,23 +715,26 @@
           <t>Software (Internet)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0738</v>
+      </c>
       <c r="G3">
-        <v>-0.9791666666666665</v>
+        <v>-0.2388379204892966</v>
       </c>
       <c r="H3">
-        <v>-1.704166666666667</v>
+        <v>-0.2395514780835882</v>
       </c>
       <c r="I3">
-        <v>-1.413308268398423</v>
+        <v>-0.2872945515353514</v>
       </c>
       <c r="J3">
-        <v>-1.413308268398423</v>
+        <v>-0.2872945515353514</v>
       </c>
       <c r="K3">
-        <v>-4.3</v>
+        <v>-2.85</v>
       </c>
       <c r="L3">
-        <v>-1.791666666666667</v>
+        <v>-0.290519877675841</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -748,59 +763,68 @@
       <c r="V3">
         <v>0</v>
       </c>
+      <c r="W3">
+        <v>-0.3421368547418968</v>
+      </c>
       <c r="X3">
-        <v>0.05946736856438736</v>
+        <v>0.1136701707817108</v>
+      </c>
+      <c r="Y3">
+        <v>-0.4558070255236075</v>
       </c>
       <c r="Z3">
-        <v>247.4425579303077</v>
+        <v>6.899715504978664</v>
       </c>
       <c r="AA3">
-        <v>-349.7126130765597</v>
+        <v>-1.982250671724356</v>
       </c>
       <c r="AB3">
-        <v>0.0594457175453639</v>
+        <v>0.1136614249837494</v>
       </c>
       <c r="AC3">
-        <v>-349.7720587941051</v>
+        <v>-2.095912096708106</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>0.009699220781075019</v>
+        <v>0.001797752808988764</v>
       </c>
       <c r="AF3">
-        <v>0.009699220781075019</v>
+        <v>0.001797752808988764</v>
       </c>
       <c r="AG3">
-        <v>0.009699220781075019</v>
+        <v>0.001797752808988764</v>
       </c>
       <c r="AH3">
-        <v>0.0006419201758652632</v>
+        <v>0.0004309300008079938</v>
       </c>
       <c r="AI3">
-        <v>0.001171446029915086</v>
+        <v>1</v>
       </c>
       <c r="AJ3">
-        <v>0.0006419201758652632</v>
+        <v>0.0004309300008079938</v>
       </c>
       <c r="AK3">
-        <v>0.001171446029915086</v>
+        <v>1</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="AM3">
-        <v>-0.05</v>
+        <v>-0.015</v>
       </c>
       <c r="AN3">
         <v>-0</v>
       </c>
+      <c r="AO3">
+        <v>-469.9999999999999</v>
+      </c>
       <c r="AP3">
-        <v>-0.004162755700032197</v>
+        <v>-0.0008735436389644139</v>
       </c>
       <c r="AQ3">
-        <v>68</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/singapore/singapore_software_internet.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_software_internet.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0738</v>
+        <v>-0.282</v>
       </c>
       <c r="G2">
-        <v>-0.2388379204892966</v>
+        <v>-0.2537037037037037</v>
       </c>
       <c r="H2">
-        <v>-0.2395514780835882</v>
+        <v>-0.2537037037037037</v>
       </c>
       <c r="I2">
-        <v>-0.2872945515353514</v>
+        <v>-0.4722222222222222</v>
       </c>
       <c r="J2">
-        <v>-0.2872945515353514</v>
+        <v>-0.4722222222222222</v>
       </c>
       <c r="K2">
-        <v>-2.85</v>
+        <v>-1.02</v>
       </c>
       <c r="L2">
-        <v>-0.290519877675841</v>
+        <v>-0.4722222222222222</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -635,68 +635,53 @@
       <c r="V2">
         <v>0</v>
       </c>
-      <c r="W2">
-        <v>-0.3421368547418968</v>
-      </c>
       <c r="X2">
-        <v>0.1136701707817108</v>
-      </c>
-      <c r="Y2">
-        <v>-0.4558070255236075</v>
-      </c>
-      <c r="Z2">
-        <v>6.899715504978664</v>
-      </c>
-      <c r="AA2">
-        <v>-1.982250671724356</v>
+        <v>0.09724085421900168</v>
       </c>
       <c r="AB2">
-        <v>0.1136614249837494</v>
-      </c>
-      <c r="AC2">
-        <v>-2.095912096708106</v>
+        <v>0.09727025603571446</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="AE2">
-        <v>0.001797752808988764</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.001797752808988764</v>
+        <v>0.015</v>
       </c>
       <c r="AG2">
-        <v>0.001797752808988764</v>
+        <v>0.015</v>
       </c>
       <c r="AH2">
-        <v>0.0004309300008079938</v>
+        <v>0.005253940455341506</v>
       </c>
       <c r="AI2">
-        <v>1</v>
+        <v>0.003064351378958121</v>
       </c>
       <c r="AJ2">
-        <v>0.0004309300008079938</v>
+        <v>0.005253940455341506</v>
       </c>
       <c r="AK2">
-        <v>1</v>
+        <v>0.003064351378958121</v>
       </c>
       <c r="AL2">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="AM2">
-        <v>-0.015</v>
+        <v>-0.017</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>-0.03036437246963563</v>
       </c>
       <c r="AO2">
-        <v>-469.9999999999999</v>
+        <v>-1020</v>
       </c>
       <c r="AP2">
-        <v>-0.0008735436389644139</v>
+        <v>-0.03036437246963563</v>
       </c>
       <c r="AQ2">
-        <v>188</v>
+        <v>60.00000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +701,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0738</v>
+        <v>-0.282</v>
       </c>
       <c r="G3">
-        <v>-0.2388379204892966</v>
+        <v>-0.2537037037037037</v>
       </c>
       <c r="H3">
-        <v>-0.2395514780835882</v>
+        <v>-0.2537037037037037</v>
       </c>
       <c r="I3">
-        <v>-0.2872945515353514</v>
+        <v>-0.4722222222222222</v>
       </c>
       <c r="J3">
-        <v>-0.2872945515353514</v>
+        <v>-0.4722222222222222</v>
       </c>
       <c r="K3">
-        <v>-2.85</v>
+        <v>-1.02</v>
       </c>
       <c r="L3">
-        <v>-0.290519877675841</v>
+        <v>-0.4722222222222222</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -763,68 +748,53 @@
       <c r="V3">
         <v>0</v>
       </c>
-      <c r="W3">
-        <v>-0.3421368547418968</v>
-      </c>
       <c r="X3">
-        <v>0.1136701707817108</v>
-      </c>
-      <c r="Y3">
-        <v>-0.4558070255236075</v>
-      </c>
-      <c r="Z3">
-        <v>6.899715504978664</v>
-      </c>
-      <c r="AA3">
-        <v>-1.982250671724356</v>
+        <v>0.09724085421900168</v>
       </c>
       <c r="AB3">
-        <v>0.1136614249837494</v>
-      </c>
-      <c r="AC3">
-        <v>-2.095912096708106</v>
+        <v>0.09727025603571446</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="AE3">
-        <v>0.001797752808988764</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.001797752808988764</v>
+        <v>0.015</v>
       </c>
       <c r="AG3">
-        <v>0.001797752808988764</v>
+        <v>0.015</v>
       </c>
       <c r="AH3">
-        <v>0.0004309300008079938</v>
+        <v>0.005253940455341506</v>
       </c>
       <c r="AI3">
-        <v>1</v>
+        <v>0.003064351378958121</v>
       </c>
       <c r="AJ3">
-        <v>0.0004309300008079938</v>
+        <v>0.005253940455341506</v>
       </c>
       <c r="AK3">
-        <v>1</v>
+        <v>0.003064351378958121</v>
       </c>
       <c r="AL3">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="AM3">
-        <v>-0.015</v>
+        <v>-0.017</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>-0.03036437246963563</v>
       </c>
       <c r="AO3">
-        <v>-469.9999999999999</v>
+        <v>-1020</v>
       </c>
       <c r="AP3">
-        <v>-0.0008735436389644139</v>
+        <v>-0.03036437246963563</v>
       </c>
       <c r="AQ3">
-        <v>188</v>
+        <v>60.00000000000001</v>
       </c>
     </row>
   </sheetData>
